--- a/campus_100_tickets.xlsx
+++ b/campus_100_tickets.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100 Campus Tickets" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="100 Dev Scaling &amp; QA Tickets" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N101"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,7049 +424,5754 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Student ID</t>
+          <t>Domain Category</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Student Name</t>
+          <t>Sub System</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Hostel Block</t>
+          <t>Priority</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Sub Category</t>
+          <t>Issue Title</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Priority</t>
+          <t>Technical Specifications &amp; Description</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Assigned Engineering Team</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Automation Automated Test Triaged</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Logged Timestamp</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Assigned Team</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>AI Triaged</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Logged Timestamp</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Resolution Note</t>
+          <t>Resolution &amp; Deployment Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TCK-1001</t>
+          <t>DEV-TCK-2001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>STU-2026-100</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Database Connection Pool</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>General Fever</t>
+          <t>Scale BigQuery / PostgreSQL connection pool for 50,000 concurrent student logins (#1)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Database connection pool saturated during morning 09:00 AM class attendance peak. Need to adjust MaxConnections to 500. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DevOps &amp; Infrastructure Team</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>High fever and shivering post-monsoon study session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Student reported 102.4°F temperature. Requested tele-consultation and fever meds. (Logged for Rohit Sharma at Hostel Block A).</t>
+          <t>2026-09-13 03:52:52</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Campus Clinical Team</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2026-09-13 03:47:34</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TCK-1002</t>
+          <t>DEV-TCK-2002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>STU-2026-101</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Redis Cache Layer</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mental Health Tele-MANAS</t>
+          <t>Implement Redis cluster caching for live wearable sensor telemetry endpoints (#2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Direct DB queries for live heart rate and step counter telemetry causing query latency. Need Redis L2 caching with 60s TTL. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Backend Engineering</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Exam anxiety &amp; acute sleep deprivation support request</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Student requested confidential 24x7 counseling via Tele-MANAS regarding end-semester stress. (Logged for Priya Patel at Hostel Block B).</t>
+          <t>2026-09-13 03:22:52</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Tele-MANAS Counseling Desk</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2026-09-13 03:02:34</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TCK-1003</t>
+          <t>DEV-TCK-2003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STU-2026-102</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ananya Deshmukh</t>
+          <t>Horizontal Pod Autoscaler</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Configure Kubernetes HPA for API Gateway under 10k RPS load (#3)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Auto-scaling trigger threshold set too high (85% CPU). Lower CPU target to 65% for instant pod spin-up. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>DevOps Team</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Allergic skin rash on arms after hostel outdoor event</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Red itchy rash spreading on forearms. Needs video evaluation with dermatologist. (Logged for Ananya Deshmukh at Hostel Block C).</t>
+          <t>2026-09-13 02:52:52</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Dermatology On-Call Doctor</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2026-09-13 02:17:34</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TCK-1004</t>
+          <t>DEV-TCK-2004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>STU-2026-103</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>CDN Asset Optimization</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Static media and bundle asset distribution via Cloudflare / CloudFront CDN (#4)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Static JS bundles exceeding 2.5MB payload on slow 3G mobile devices. Implement Brotli compression &amp; CDN edge caching. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Frontend Performance Team</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Severe dry eye &amp; screen glare fatigue after 10hr coding session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Eye strain and burning sensation. Needs artificial tear prescription. (Logged for Rahul Verma at Hostel Block D).</t>
+          <t>2026-09-13 02:22:52</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Digital Ergonomics Desk</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2026-09-13 01:32:34</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TCK-1005</t>
+          <t>DEV-TCK-2005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>STU-2026-104</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Mehta</t>
+          <t>WebSocket Heartbeat</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orthopedics</t>
+          <t>Real-time vitals camera streaming WebSocket socket reconnection stability (#5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>WebSocket connections dropping after 5 minutes of idle posture coaching. Implement exponential backoff ping/pong heartbeat. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Realtime WebSockets Team</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sprained ankle during campus badminton tournament</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Swollen right ankle. Requested cold compress guidance and X-ray slot. (Logged for Aarav Mehta at PG Residence 1).</t>
+          <t>2026-09-13 01:52:52</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sports Medicine Unit</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2026-09-13 00:47:34</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TCK-1006</t>
+          <t>DEV-TCK-2006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>STU-2026-105</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Sneha Kulkarni</t>
+          <t>Playwright E2E Automation</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Heart Rate Alert</t>
+          <t>Playwright End-to-End browser test suite failing on Signup Step 6 Plan Selection (#6)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Automated Playwright test `tests/e2e/signup_flow.spec.ts` failed due to missing plan selection modal selector `#plan-c-btn`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>QA Automation Team</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Resting Heart Rate Spike (138 BPM) detected by Smart Watch</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wearable sensor triggered resting tachycardia alert while student was seated in library. (Logged for Sneha Kulkarni at Married Scholar Quarters).</t>
+          <t>2026-09-13 01:22:52</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Vitals Monitoring AI</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2026-09-13 00:02:34</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TCK-1007</t>
+          <t>DEV-TCK-2007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>STU-2026-106</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>Vitest Coverage Gate</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SpO2 Telemetry</t>
+          <t>Vitest unit test coverage dropped below mandatory 85% threshold (#7)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>New health overview telemetry module added without unit test assertions. Need 100% coverage on `healthExperience.ts`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>QA Quality Engineers</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Low Blood Oxygen SpO2 (92%) alert during night study</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RPPG Vitals Camera &amp; Wearables flagged drop in peripheral oxygen saturation. (Logged for Vikram Singh at Hostel Block A).</t>
+          <t>2026-09-13 00:52:52</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Emergency Response Desk</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2026-09-12 23:17:34</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TCK-1008</t>
+          <t>DEV-TCK-2008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>STU-2026-107</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kavya Nair</t>
+          <t>API Contract Testing</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>ESCALATED</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Posture Coach</t>
+          <t>OpenAPI schema validation mismatch on POST /api/v1/telemetry/vitals endpoint (#8)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Contract test flagged missing `sensorAccuracyIndex` field in JSON request payload. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ESCALATED</t>
+          <t>Backend QA Team</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Chronic Slouch Posture warning (3.5 hours continuous neck tilt)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Study Posture Coach sensor alerted lumbar strain risk during project coding. (Logged for Kavya Nair at Hostel Block B).</t>
+          <t>2026-09-13 00:22:52</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Student Wellness AI</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2026-09-12 22:32:34</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TCK-1009</t>
+          <t>DEV-TCK-2009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>STU-2026-108</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Devansh Gupta</t>
+          <t>Mock Service Worker (MSW)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Step Counter</t>
+          <t>MSW mock server latency simulation for offline mode PWA testing (#9)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Mock service worker failing to intercept offline PWA sync requests in Vitest runner. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>QA Tooling Team</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Zero mobility alert (Under 500 steps for 48 hours straight)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Mobile Step Counter sensor flagged severe sedentary lock during exam preparation. (Logged for Devansh Gupta at Hostel Block C).</t>
+          <t>2026-09-12 23:52:52</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Health Coach Agent</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2026-09-12 21:47:34</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TCK-1010</t>
+          <t>DEV-TCK-2010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>STU-2026-109</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Isha Sundaram</t>
+          <t>Visual Regression Test</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monsoon Dengue NS1</t>
+          <t>Percy / Chromatic visual regression diff detected on InterfaceBar theme header (#10)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Dark mode pill buttons shifted 2px out of alignment on 1440px viewport displays. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Frontend QA Team</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>NABL Dengue NS1 Antigen &amp; Complete Blood Count (CBC) home sample collection</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Fever suspect requested hostel room sample collection for CBC platelet count check. (Logged for Isha Sundaram at Hostel Block D).</t>
+          <t>2026-09-12 23:22:52</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Pathology Lab Partner</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-09-12 21:02:34</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TCK-1011</t>
+          <t>DEV-TCK-2011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>STU-2026-110</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Crisis Gate Safety</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitamin D3 &amp; B12</t>
+          <t>Crisis Gate AI deterministic bypass latency under 10ms for URGENT_EMERGENCY prompts (#11)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Crisis detection gate must process self-harm / panic keywords strictly on-device in &lt;10ms without hitting remote LLM. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>AI Safety &amp; Ethics Team</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Routine Vitamin D3 &amp; Serum B12 deficiency panel booking</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Student booked discounted lab package under Studentkare Plan B membership. (Logged for Arjun Reddy at PG Residence 1).</t>
+          <t>2026-09-12 22:52:52</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Diagnostic Services Unit</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-09-12 20:17:34</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TCK-1012</t>
+          <t>DEV-TCK-2012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>STU-2026-111</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Meera Rao</t>
+          <t>AI Voice Prescription</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Water Bacteria Test</t>
+          <t>Optimize Speech-to-Text Whisper model latency for medical dosage parsing (#12)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Voice prescription recording parsing taking &gt;3.2 seconds. Need streaming chunk parsing via WebSockets. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Speech Team</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Hostel Block C Water Dispenser Bacterial Culture Test</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Randomized 4-hour water sample collected to verify E. coli and coliform absence. (Logged for Meera Rao at Married Scholar Quarters).</t>
+          <t>2026-09-12 22:22:52</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Environmental Safety Lab</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>2026-09-12 19:32:34</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TCK-1013</t>
+          <t>DEV-TCK-2013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>STU-2026-112</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Siddharth Joshi</t>
+          <t>RAG Vector Store</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SANITATION_FACILITIES</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Water Purifier</t>
+          <t>Vector DB embedding index sync for 1,000+ medical guidelines &amp; drug interactions (#13)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Pinecone / Qdrant vector index out of sync with new NABL lab test reference values. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>AI Data Engineering</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hostel Block B 2nd Floor RO UV Filter replacement required</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Sanitation sensor indicated UV lamp intensity drop below safety threshold. (Logged for Siddharth Joshi at Hostel Block A).</t>
+          <t>2026-09-12 21:52:52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Hostel Maintenance Operations</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2026-09-12 18:47:34</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TCK-1014</t>
+          <t>DEV-TCK-2014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>STU-2026-113</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tanvi Saxena</t>
+          <t>Prompt Injection Defense</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SANITATION_FACILITIES</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>Harden AI Health Assistant system prompt against jailbreak injection attacks (#14)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Red team security scan identified prompt bypass attempt targeting system constitution rules. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Security Team</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Mosquito breeding inspection requested around PG Residence garden</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Stagnant water near cooler drain pipes needs immediate fogging and larvicide treatment. (Logged for Tanvi Saxena at Hostel Block B).</t>
+          <t>2026-09-12 21:22:52</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Campus Sanitation Squad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-09-12 18:02:34</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TCK-1015</t>
+          <t>DEV-TCK-2015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>STU-2026-114</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Karan Bhatia</t>
+          <t>LLM Token Budget</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PHARMACY_MEDS</t>
+          <t>ESCALATED</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>AI Voice Prescription</t>
+          <t>Implement token capping and fallback model switching (Gemini Pro to Flash) (#15)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>High token consumption on long multi-turn patient chats. Implement auto-summarization at 4,000 tokens. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>ESCALATED</t>
+          <t>AI Infra Team</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Fulfillment of AI Voice-Parsed Prescription for Anti-Histamines &amp; Paracetamol</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Prescription parsed via AI Voice Modal. Requested hostel room delivery. (Logged for Karan Bhatia at Hostel Block C).</t>
+          <t>2026-09-12 20:52:52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Campus Dispensary Pharmacy</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-09-12 17:17:34</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TCK-1016</t>
+          <t>DEV-TCK-2016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>STU-2026-115</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Riya Sen</t>
+          <t>4-Hr Scouting Agent Cron</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>PHARMACY_MEDS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cold Chain Insulin</t>
+          <t>4-Hour AI Scouting Agent background cron schedule execution monitoring (#16)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Background schedule task `task-524` verified running on `0 */4 * * *` cron schedule pulling campus telemetry. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Automation &amp; Agent Ops</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Cold-chain storage verification for student diabetes medication</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Insulin pen storage check at hostel pharmacy refrigeration unit. (Logged for Riya Sen at Hostel Block D).</t>
+          <t>2026-09-12 20:22:52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pharmacy Cold Chain Desk</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2026-09-12 16:32:34</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TCK-1017</t>
+          <t>DEV-TCK-2017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STU-2026-116</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Aditya Iyer</t>
+          <t>GitHub Actions CI Gate</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>INSURANCE_CLAIMS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plan B Reimbursement</t>
+          <t>GitHub Actions CI pipeline execution time optimization (Reduce from 8m to 2m) (#17)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Cache node_modules and Vitest transform files to accelerate pull request quality gate checks. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>DevOps &amp; CI/CD Team</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Insurance claim adjudication for outpatient emergency clinic visit</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Student submitted ₹1,200 emergency OPD consultation receipt for Plan B 100% claim settlement. (Logged for Aditya Iyer at PG Residence 1).</t>
+          <t>2026-09-12 19:52:52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Insurance Adjudication AI</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2026-09-12 15:47:34</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TCK-1018</t>
+          <t>DEV-TCK-2018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>STU-2026-117</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Nisha Banerjee</t>
+          <t>Knip Dead Code Audit</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>INSURANCE_CLAIMS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Claim Anomaly Review</t>
+          <t>Automated Knip static analysis flagged 14 unused exports in legacy components (#18)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Run `knip --no-exit-code` and tree-shake unused mock data structures to reduce bundle size by 120KB. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Code Quality Team</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Duplicate bill anomaly flagged on hospitalization claim</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Claim Adjudication AI flagged potential double-entry invoice for review by signed officer. (Logged for Nisha Banerjee at Married Scholar Quarters).</t>
+          <t>2026-09-12 19:22:52</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Claims Compliance Officer</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2026-09-12 15:02:34</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TCK-1019</t>
+          <t>DEV-TCK-2019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>STU-2026-118</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Tarun Chawla</t>
+          <t>Semgrep SAST Security</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>EMERGENCY_SOS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ambulance Dispatch</t>
+          <t>Semgrep security rule scanner flagged potential XSS target in unescaped innerHTML (#19)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Static analysis identified unescaped user note rendering in legacy support widget. Replace with DOMPurify. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Application Security Team</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Emergency 24x7 Ambulance dispatch request for acute abdominal distress</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Student triggered 24x7 SOS emergency button. Campus medical team dispatched to Hostel Block A. (Logged for Tarun Chawla at Hostel Block A).</t>
+          <t>2026-09-12 18:52:52</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>24x7 Emergency Dispatch Unit</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2026-09-12 14:17:34</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TCK-1020</t>
+          <t>DEV-TCK-2020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>STU-2026-119</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pooja Agarwal</t>
+          <t>OWASP ZAP DAST Scan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EMERGENCY_SOS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Crisis Intervention</t>
+          <t>OWASP ZAP dynamic application security test scan report remediation (#20)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Automated DAST scan flagged missing Strict-Transport-Security (HSTS) header on staging deployment. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>SecOps Team</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Panic attack emergency trigger from central library reading room</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>SOS trigger handled by Triage Council AI. Campus counselor dispatched. (Logged for Pooja Agarwal at Hostel Block B).</t>
+          <t>2026-09-12 18:22:52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Crisis Response Team</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2026-09-12 13:32:34</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TCK-1021</t>
+          <t>DEV-TCK-2021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>STU-2026-120</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Database Connection Pool</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI_DIAGNOSTICS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4-Hr Scouting Anomaly</t>
+          <t>Scale BigQuery / PostgreSQL connection pool for 50,000 concurrent student logins (#21)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Database connection pool saturated during morning 09:00 AM class attendance peak. Need to adjust MaxConnections to 500. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DevOps &amp; Infrastructure Team</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>4-Hour Scouting Loop Flagged Seasonal Flu Spike in Hostel Block D</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Automated 4-hour agent scouting loop detected 4 viral flu cases in 12 hours. (Logged for Rohit Sharma at Hostel Block C).</t>
+          <t>2026-09-12 17:52:52</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Automated 4-Hr Agent Loop</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2026-09-12 12:47:34</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TCK-1022</t>
+          <t>DEV-TCK-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>STU-2026-121</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Redis Cache Layer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI_DIAGNOSTICS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Weather Alert Sync</t>
+          <t>Implement Redis cluster caching for live wearable sensor telemetry endpoints (#22)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Direct DB queries for live heart rate and step counter telemetry causing query latency. Need Redis L2 caching with 60s TTL. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Backend Engineering</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Monsoon High Humidity Weather Banner Triggered automatically</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Weather API updated microclimate alert to 85% humidity Dengue risk. (Logged for Priya Patel at Hostel Block D).</t>
+          <t>2026-09-12 17:22:52</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Environmental Sensing Agent</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2026-09-12 12:02:34</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TCK-1023</t>
+          <t>DEV-TCK-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>STU-2026-122</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ananya Deshmukh</t>
+          <t>Horizontal Pod Autoscaler</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>General Fever</t>
+          <t>Configure Kubernetes HPA for API Gateway under 10k RPS load (#23)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Auto-scaling trigger threshold set too high (85% CPU). Lower CPU target to 65% for instant pod spin-up. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>DevOps Team</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>High fever and shivering post-monsoon study session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Student reported 102.4°F temperature. Requested tele-consultation and fever meds. (Logged for Ananya Deshmukh at PG Residence 1).</t>
+          <t>2026-09-12 16:52:52</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Campus Clinical Team</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>2026-09-12 11:17:34</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TCK-1024</t>
+          <t>DEV-TCK-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>STU-2026-123</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>CDN Asset Optimization</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mental Health Tele-MANAS</t>
+          <t>Static media and bundle asset distribution via Cloudflare / CloudFront CDN (#24)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Static JS bundles exceeding 2.5MB payload on slow 3G mobile devices. Implement Brotli compression &amp; CDN edge caching. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Frontend Performance Team</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Exam anxiety &amp; acute sleep deprivation support request</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Student requested confidential 24x7 counseling via Tele-MANAS regarding end-semester stress. (Logged for Rahul Verma at Married Scholar Quarters).</t>
+          <t>2026-09-12 16:22:52</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Tele-MANAS Counseling Desk</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>2026-09-12 10:32:34</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TCK-1025</t>
+          <t>DEV-TCK-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>STU-2026-124</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Aarav Mehta</t>
+          <t>WebSocket Heartbeat</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Real-time vitals camera streaming WebSocket socket reconnection stability (#25)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>WebSocket connections dropping after 5 minutes of idle posture coaching. Implement exponential backoff ping/pong heartbeat. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Realtime WebSockets Team</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Allergic skin rash on arms after hostel outdoor event</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Red itchy rash spreading on forearms. Needs video evaluation with dermatologist. (Logged for Aarav Mehta at Hostel Block A).</t>
+          <t>2026-09-12 15:52:52</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Dermatology On-Call Doctor</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>2026-09-12 09:47:34</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TCK-1026</t>
+          <t>DEV-TCK-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>STU-2026-125</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sneha Kulkarni</t>
+          <t>Playwright E2E Automation</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Playwright End-to-End browser test suite failing on Signup Step 6 Plan Selection (#26)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Automated Playwright test `tests/e2e/signup_flow.spec.ts` failed due to missing plan selection modal selector `#plan-c-btn`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>QA Automation Team</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Severe dry eye &amp; screen glare fatigue after 10hr coding session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Eye strain and burning sensation. Needs artificial tear prescription. (Logged for Sneha Kulkarni at Hostel Block B).</t>
+          <t>2026-09-12 15:22:52</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Digital Ergonomics Desk</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>2026-09-12 09:02:34</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TCK-1027</t>
+          <t>DEV-TCK-2027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>STU-2026-126</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>Vitest Coverage Gate</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orthopedics</t>
+          <t>Vitest unit test coverage dropped below mandatory 85% threshold (#27)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>New health overview telemetry module added without unit test assertions. Need 100% coverage on `healthExperience.ts`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>QA Quality Engineers</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sprained ankle during campus badminton tournament</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Swollen right ankle. Requested cold compress guidance and X-ray slot. (Logged for Vikram Singh at Hostel Block C).</t>
+          <t>2026-09-12 14:52:52</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Sports Medicine Unit</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>2026-09-12 08:17:34</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TCK-1028</t>
+          <t>DEV-TCK-2028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>STU-2026-127</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Kavya Nair</t>
+          <t>API Contract Testing</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Heart Rate Alert</t>
+          <t>OpenAPI schema validation mismatch on POST /api/v1/telemetry/vitals endpoint (#28)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Contract test flagged missing `sensorAccuracyIndex` field in JSON request payload. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Backend QA Team</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Resting Heart Rate Spike (138 BPM) detected by Smart Watch</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Wearable sensor triggered resting tachycardia alert while student was seated in library. (Logged for Kavya Nair at Hostel Block D).</t>
+          <t>2026-09-12 14:22:52</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Vitals Monitoring AI</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>2026-09-12 07:32:34</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TCK-1029</t>
+          <t>DEV-TCK-2029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>STU-2026-128</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Devansh Gupta</t>
+          <t>Mock Service Worker (MSW)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>SpO2 Telemetry</t>
+          <t>MSW mock server latency simulation for offline mode PWA testing (#29)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Mock service worker failing to intercept offline PWA sync requests in Vitest runner. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>ESCALATED</t>
+          <t>QA Tooling Team</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Low Blood Oxygen SpO2 (92%) alert during night study</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>RPPG Vitals Camera &amp; Wearables flagged drop in peripheral oxygen saturation. (Logged for Devansh Gupta at PG Residence 1).</t>
+          <t>2026-09-12 13:52:52</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Emergency Response Desk</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>2026-09-12 06:47:34</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TCK-1030</t>
+          <t>DEV-TCK-2030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>STU-2026-129</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Isha Sundaram</t>
+          <t>Visual Regression Test</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Posture Coach</t>
+          <t>Percy / Chromatic visual regression diff detected on InterfaceBar theme header (#30)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Dark mode pill buttons shifted 2px out of alignment on 1440px viewport displays. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Frontend QA Team</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Chronic Slouch Posture warning (3.5 hours continuous neck tilt)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Study Posture Coach sensor alerted lumbar strain risk during project coding. (Logged for Isha Sundaram at Married Scholar Quarters).</t>
+          <t>2026-09-12 13:22:52</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Student Wellness AI</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>2026-09-12 06:02:34</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TCK-1031</t>
+          <t>DEV-TCK-2031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>STU-2026-130</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Crisis Gate Safety</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Step Counter</t>
+          <t>Crisis Gate AI deterministic bypass latency under 10ms for URGENT_EMERGENCY prompts (#31)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Crisis detection gate must process self-harm / panic keywords strictly on-device in &lt;10ms without hitting remote LLM. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>AI Safety &amp; Ethics Team</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Zero mobility alert (Under 500 steps for 48 hours straight)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Mobile Step Counter sensor flagged severe sedentary lock during exam preparation. (Logged for Arjun Reddy at Hostel Block A).</t>
+          <t>2026-09-12 12:52:52</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Health Coach Agent</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>2026-09-12 05:17:34</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TCK-1032</t>
+          <t>DEV-TCK-2032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>STU-2026-131</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Meera Rao</t>
+          <t>AI Voice Prescription</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monsoon Dengue NS1</t>
+          <t>Optimize Speech-to-Text Whisper model latency for medical dosage parsing (#32)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Voice prescription recording parsing taking &gt;3.2 seconds. Need streaming chunk parsing via WebSockets. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Speech Team</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>NABL Dengue NS1 Antigen &amp; Complete Blood Count (CBC) home sample collection</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Fever suspect requested hostel room sample collection for CBC platelet count check. (Logged for Meera Rao at Hostel Block B).</t>
+          <t>2026-09-12 12:22:52</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Pathology Lab Partner</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>2026-09-12 04:32:34</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TCK-1033</t>
+          <t>DEV-TCK-2033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>STU-2026-132</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Siddharth Joshi</t>
+          <t>RAG Vector Store</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vitamin D3 &amp; B12</t>
+          <t>Vector DB embedding index sync for 1,000+ medical guidelines &amp; drug interactions (#33)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Pinecone / Qdrant vector index out of sync with new NABL lab test reference values. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Data Engineering</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Routine Vitamin D3 &amp; Serum B12 deficiency panel booking</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Student booked discounted lab package under Studentkare Plan B membership. (Logged for Siddharth Joshi at Hostel Block C).</t>
+          <t>2026-09-12 11:52:52</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Diagnostic Services Unit</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>2026-09-12 03:47:34</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TCK-1034</t>
+          <t>DEV-TCK-2034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>STU-2026-133</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tanvi Saxena</t>
+          <t>Prompt Injection Defense</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Water Bacteria Test</t>
+          <t>Harden AI Health Assistant system prompt against jailbreak injection attacks (#34)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Red team security scan identified prompt bypass attempt targeting system constitution rules. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>AI Security Team</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Hostel Block C Water Dispenser Bacterial Culture Test</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Randomized 4-hour water sample collected to verify E. coli and coliform absence. (Logged for Tanvi Saxena at Hostel Block D).</t>
+          <t>2026-09-12 11:22:52</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Environmental Safety Lab</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>2026-09-12 03:02:34</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TCK-1035</t>
+          <t>DEV-TCK-2035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>STU-2026-134</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Karan Bhatia</t>
+          <t>LLM Token Budget</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SANITATION_FACILITIES</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Water Purifier</t>
+          <t>Implement token capping and fallback model switching (Gemini Pro to Flash) (#35)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>High token consumption on long multi-turn patient chats. Implement auto-summarization at 4,000 tokens. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Infra Team</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Hostel Block B 2nd Floor RO UV Filter replacement required</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Sanitation sensor indicated UV lamp intensity drop below safety threshold. (Logged for Karan Bhatia at PG Residence 1).</t>
+          <t>2026-09-12 10:52:52</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Hostel Maintenance Operations</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>2026-09-12 02:17:34</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TCK-1036</t>
+          <t>DEV-TCK-2036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>STU-2026-135</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Riya Sen</t>
+          <t>4-Hr Scouting Agent Cron</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SANITATION_FACILITIES</t>
+          <t>ESCALATED</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>4-Hour AI Scouting Agent background cron schedule execution monitoring (#36)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Background schedule task `task-524` verified running on `0 */4 * * *` cron schedule pulling campus telemetry. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Automation &amp; Agent Ops</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Mosquito breeding inspection requested around PG Residence garden</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Stagnant water near cooler drain pipes needs immediate fogging and larvicide treatment. (Logged for Riya Sen at Married Scholar Quarters).</t>
+          <t>2026-09-12 10:22:52</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Campus Sanitation Squad</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>2026-09-12 01:32:34</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TCK-1037</t>
+          <t>DEV-TCK-2037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>STU-2026-136</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Aditya Iyer</t>
+          <t>GitHub Actions CI Gate</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PHARMACY_MEDS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AI Voice Prescription</t>
+          <t>GitHub Actions CI pipeline execution time optimization (Reduce from 8m to 2m) (#37)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Cache node_modules and Vitest transform files to accelerate pull request quality gate checks. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>DevOps &amp; CI/CD Team</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Fulfillment of AI Voice-Parsed Prescription for Anti-Histamines &amp; Paracetamol</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Prescription parsed via AI Voice Modal. Requested hostel room delivery. (Logged for Aditya Iyer at Hostel Block A).</t>
+          <t>2026-09-12 09:52:52</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Campus Dispensary Pharmacy</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>2026-09-12 00:47:34</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TCK-1038</t>
+          <t>DEV-TCK-2038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>STU-2026-137</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nisha Banerjee</t>
+          <t>Knip Dead Code Audit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>PHARMACY_MEDS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cold Chain Insulin</t>
+          <t>Automated Knip static analysis flagged 14 unused exports in legacy components (#38)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Run `knip --no-exit-code` and tree-shake unused mock data structures to reduce bundle size by 120KB. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Code Quality Team</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Cold-chain storage verification for student diabetes medication</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Insulin pen storage check at hostel pharmacy refrigeration unit. (Logged for Nisha Banerjee at Hostel Block B).</t>
+          <t>2026-09-12 09:22:52</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Pharmacy Cold Chain Desk</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>2026-09-12 00:02:34</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TCK-1039</t>
+          <t>DEV-TCK-2039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>STU-2026-138</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tarun Chawla</t>
+          <t>Semgrep SAST Security</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>INSURANCE_CLAIMS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plan B Reimbursement</t>
+          <t>Semgrep security rule scanner flagged potential XSS target in unescaped innerHTML (#39)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Static analysis identified unescaped user note rendering in legacy support widget. Replace with DOMPurify. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Application Security Team</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Insurance claim adjudication for outpatient emergency clinic visit</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Student submitted ₹1,200 emergency OPD consultation receipt for Plan B 100% claim settlement. (Logged for Tarun Chawla at Hostel Block C).</t>
+          <t>2026-09-12 08:52:52</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Insurance Adjudication AI</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>2026-09-11 23:17:34</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TCK-1040</t>
+          <t>DEV-TCK-2040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>STU-2026-139</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pooja Agarwal</t>
+          <t>OWASP ZAP DAST Scan</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>INSURANCE_CLAIMS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Claim Anomaly Review</t>
+          <t>OWASP ZAP dynamic application security test scan report remediation (#40)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Automated DAST scan flagged missing Strict-Transport-Security (HSTS) header on staging deployment. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>SecOps Team</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Duplicate bill anomaly flagged on hospitalization claim</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Claim Adjudication AI flagged potential double-entry invoice for review by signed officer. (Logged for Pooja Agarwal at Hostel Block D).</t>
+          <t>2026-09-12 08:22:52</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Claims Compliance Officer</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>2026-09-11 22:32:34</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TCK-1041</t>
+          <t>DEV-TCK-2041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>STU-2026-140</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Database Connection Pool</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EMERGENCY_SOS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ambulance Dispatch</t>
+          <t>Scale BigQuery / PostgreSQL connection pool for 50,000 concurrent student logins (#41)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Database connection pool saturated during morning 09:00 AM class attendance peak. Need to adjust MaxConnections to 500. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DevOps &amp; Infrastructure Team</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Emergency 24x7 Ambulance dispatch request for acute abdominal distress</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Student triggered 24x7 SOS emergency button. Campus medical team dispatched to Hostel Block A. (Logged for Rohit Sharma at PG Residence 1).</t>
+          <t>2026-09-12 07:52:52</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>24x7 Emergency Dispatch Unit</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>2026-09-11 21:47:34</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TCK-1042</t>
+          <t>DEV-TCK-2042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>STU-2026-141</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Redis Cache Layer</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>EMERGENCY_SOS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Crisis Intervention</t>
+          <t>Implement Redis cluster caching for live wearable sensor telemetry endpoints (#42)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Direct DB queries for live heart rate and step counter telemetry causing query latency. Need Redis L2 caching with 60s TTL. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Backend Engineering</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Panic attack emergency trigger from central library reading room</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>SOS trigger handled by Triage Council AI. Campus counselor dispatched. (Logged for Priya Patel at Married Scholar Quarters).</t>
+          <t>2026-09-12 07:22:52</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Crisis Response Team</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>2026-09-11 21:02:34</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TCK-1043</t>
+          <t>DEV-TCK-2043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>STU-2026-142</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ananya Deshmukh</t>
+          <t>Horizontal Pod Autoscaler</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AI_DIAGNOSTICS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>4-Hr Scouting Anomaly</t>
+          <t>Configure Kubernetes HPA for API Gateway under 10k RPS load (#43)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Auto-scaling trigger threshold set too high (85% CPU). Lower CPU target to 65% for instant pod spin-up. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>DevOps Team</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>4-Hour Scouting Loop Flagged Seasonal Flu Spike in Hostel Block D</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Automated 4-hour agent scouting loop detected 4 viral flu cases in 12 hours. (Logged for Ananya Deshmukh at Hostel Block A).</t>
+          <t>2026-09-12 06:52:52</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Automated 4-Hr Agent Loop</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>2026-09-11 20:17:34</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TCK-1044</t>
+          <t>DEV-TCK-2044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>STU-2026-143</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>CDN Asset Optimization</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AI_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Weather Alert Sync</t>
+          <t>Static media and bundle asset distribution via Cloudflare / CloudFront CDN (#44)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Static JS bundles exceeding 2.5MB payload on slow 3G mobile devices. Implement Brotli compression &amp; CDN edge caching. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Frontend Performance Team</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Monsoon High Humidity Weather Banner Triggered automatically</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Weather API updated microclimate alert to 85% humidity Dengue risk. (Logged for Rahul Verma at Hostel Block B).</t>
+          <t>2026-09-12 06:22:52</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Environmental Sensing Agent</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>2026-09-11 19:32:34</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TCK-1045</t>
+          <t>DEV-TCK-2045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>STU-2026-144</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Aarav Mehta</t>
+          <t>WebSocket Heartbeat</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>General Fever</t>
+          <t>Real-time vitals camera streaming WebSocket socket reconnection stability (#45)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>WebSocket connections dropping after 5 minutes of idle posture coaching. Implement exponential backoff ping/pong heartbeat. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Realtime WebSockets Team</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>High fever and shivering post-monsoon study session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Student reported 102.4°F temperature. Requested tele-consultation and fever meds. (Logged for Aarav Mehta at Hostel Block C).</t>
+          <t>2026-09-12 05:52:52</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Campus Clinical Team</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>2026-09-11 18:47:34</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TCK-1046</t>
+          <t>DEV-TCK-2046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>STU-2026-145</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sneha Kulkarni</t>
+          <t>Playwright E2E Automation</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mental Health Tele-MANAS</t>
+          <t>Playwright End-to-End browser test suite failing on Signup Step 6 Plan Selection (#46)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Automated Playwright test `tests/e2e/signup_flow.spec.ts` failed due to missing plan selection modal selector `#plan-c-btn`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>QA Automation Team</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Exam anxiety &amp; acute sleep deprivation support request</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Student requested confidential 24x7 counseling via Tele-MANAS regarding end-semester stress. (Logged for Sneha Kulkarni at Hostel Block D).</t>
+          <t>2026-09-12 05:22:52</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Tele-MANAS Counseling Desk</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>2026-09-11 18:02:34</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TCK-1047</t>
+          <t>DEV-TCK-2047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>STU-2026-146</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>Vitest Coverage Gate</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Vitest unit test coverage dropped below mandatory 85% threshold (#47)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>New health overview telemetry module added without unit test assertions. Need 100% coverage on `healthExperience.ts`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>QA Quality Engineers</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Allergic skin rash on arms after hostel outdoor event</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Red itchy rash spreading on forearms. Needs video evaluation with dermatologist. (Logged for Vikram Singh at PG Residence 1).</t>
+          <t>2026-09-12 04:52:52</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Dermatology On-Call Doctor</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>2026-09-11 17:17:34</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TCK-1048</t>
+          <t>DEV-TCK-2048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>STU-2026-147</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Kavya Nair</t>
+          <t>API Contract Testing</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>OpenAPI schema validation mismatch on POST /api/v1/telemetry/vitals endpoint (#48)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Contract test flagged missing `sensorAccuracyIndex` field in JSON request payload. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Backend QA Team</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Severe dry eye &amp; screen glare fatigue after 10hr coding session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Eye strain and burning sensation. Needs artificial tear prescription. (Logged for Kavya Nair at Married Scholar Quarters).</t>
+          <t>2026-09-12 04:22:52</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Digital Ergonomics Desk</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>2026-09-11 16:32:34</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TCK-1049</t>
+          <t>DEV-TCK-2049</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>STU-2026-148</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Devansh Gupta</t>
+          <t>Mock Service Worker (MSW)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Orthopedics</t>
+          <t>MSW mock server latency simulation for offline mode PWA testing (#49)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Mock service worker failing to intercept offline PWA sync requests in Vitest runner. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>QA Tooling Team</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Sprained ankle during campus badminton tournament</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Swollen right ankle. Requested cold compress guidance and X-ray slot. (Logged for Devansh Gupta at Hostel Block A).</t>
+          <t>2026-09-12 03:52:52</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Sports Medicine Unit</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:47:34</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TCK-1050</t>
+          <t>DEV-TCK-2050</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>STU-2026-149</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Isha Sundaram</t>
+          <t>Visual Regression Test</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>ESCALATED</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Heart Rate Alert</t>
+          <t>Percy / Chromatic visual regression diff detected on InterfaceBar theme header (#50)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Dark mode pill buttons shifted 2px out of alignment on 1440px viewport displays. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>ESCALATED</t>
+          <t>Frontend QA Team</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Resting Heart Rate Spike (138 BPM) detected by Smart Watch</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Wearable sensor triggered resting tachycardia alert while student was seated in library. (Logged for Isha Sundaram at Hostel Block B).</t>
+          <t>2026-09-12 03:22:52</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Vitals Monitoring AI</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>2026-09-11 15:02:34</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TCK-1051</t>
+          <t>DEV-TCK-2051</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>STU-2026-150</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Crisis Gate Safety</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>SpO2 Telemetry</t>
+          <t>Crisis Gate AI deterministic bypass latency under 10ms for URGENT_EMERGENCY prompts (#51)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Crisis detection gate must process self-harm / panic keywords strictly on-device in &lt;10ms without hitting remote LLM. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>AI Safety &amp; Ethics Team</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Low Blood Oxygen SpO2 (92%) alert during night study</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>RPPG Vitals Camera &amp; Wearables flagged drop in peripheral oxygen saturation. (Logged for Arjun Reddy at Hostel Block C).</t>
+          <t>2026-09-12 02:52:52</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Emergency Response Desk</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>2026-09-11 14:17:34</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TCK-1052</t>
+          <t>DEV-TCK-2052</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>STU-2026-151</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Meera Rao</t>
+          <t>AI Voice Prescription</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Posture Coach</t>
+          <t>Optimize Speech-to-Text Whisper model latency for medical dosage parsing (#52)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Voice prescription recording parsing taking &gt;3.2 seconds. Need streaming chunk parsing via WebSockets. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>AI Speech Team</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Chronic Slouch Posture warning (3.5 hours continuous neck tilt)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Study Posture Coach sensor alerted lumbar strain risk during project coding. (Logged for Meera Rao at Hostel Block D).</t>
+          <t>2026-09-12 02:22:52</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Student Wellness AI</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>2026-09-11 13:32:34</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TCK-1053</t>
+          <t>DEV-TCK-2053</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>STU-2026-152</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Siddharth Joshi</t>
+          <t>RAG Vector Store</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Step Counter</t>
+          <t>Vector DB embedding index sync for 1,000+ medical guidelines &amp; drug interactions (#53)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Pinecone / Qdrant vector index out of sync with new NABL lab test reference values. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Data Engineering</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Zero mobility alert (Under 500 steps for 48 hours straight)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Mobile Step Counter sensor flagged severe sedentary lock during exam preparation. (Logged for Siddharth Joshi at PG Residence 1).</t>
+          <t>2026-09-12 01:52:52</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Health Coach Agent</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>2026-09-11 12:47:34</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TCK-1054</t>
+          <t>DEV-TCK-2054</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>STU-2026-153</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tanvi Saxena</t>
+          <t>Prompt Injection Defense</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Monsoon Dengue NS1</t>
+          <t>Harden AI Health Assistant system prompt against jailbreak injection attacks (#54)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Red team security scan identified prompt bypass attempt targeting system constitution rules. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Security Team</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NABL Dengue NS1 Antigen &amp; Complete Blood Count (CBC) home sample collection</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Fever suspect requested hostel room sample collection for CBC platelet count check. (Logged for Tanvi Saxena at Married Scholar Quarters).</t>
+          <t>2026-09-12 01:22:52</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Pathology Lab Partner</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>2026-09-11 12:02:34</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TCK-1055</t>
+          <t>DEV-TCK-2055</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>STU-2026-154</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Karan Bhatia</t>
+          <t>LLM Token Budget</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vitamin D3 &amp; B12</t>
+          <t>Implement token capping and fallback model switching (Gemini Pro to Flash) (#55)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>High token consumption on long multi-turn patient chats. Implement auto-summarization at 4,000 tokens. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>AI Infra Team</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Routine Vitamin D3 &amp; Serum B12 deficiency panel booking</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Student booked discounted lab package under Studentkare Plan B membership. (Logged for Karan Bhatia at Hostel Block A).</t>
+          <t>2026-09-12 00:52:52</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Diagnostic Services Unit</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>2026-09-11 11:17:34</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TCK-1056</t>
+          <t>DEV-TCK-2056</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>STU-2026-155</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Riya Sen</t>
+          <t>4-Hr Scouting Agent Cron</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Water Bacteria Test</t>
+          <t>4-Hour AI Scouting Agent background cron schedule execution monitoring (#56)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Background schedule task `task-524` verified running on `0 */4 * * *` cron schedule pulling campus telemetry. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Automation &amp; Agent Ops</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Hostel Block C Water Dispenser Bacterial Culture Test</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Randomized 4-hour water sample collected to verify E. coli and coliform absence. (Logged for Riya Sen at Hostel Block B).</t>
+          <t>2026-09-12 00:22:52</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Environmental Safety Lab</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>2026-09-11 10:32:34</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TCK-1057</t>
+          <t>DEV-TCK-2057</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>STU-2026-156</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Aditya Iyer</t>
+          <t>GitHub Actions CI Gate</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SANITATION_FACILITIES</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Water Purifier</t>
+          <t>GitHub Actions CI pipeline execution time optimization (Reduce from 8m to 2m) (#57)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Cache node_modules and Vitest transform files to accelerate pull request quality gate checks. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>ESCALATED</t>
+          <t>DevOps &amp; CI/CD Team</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Hostel Block B 2nd Floor RO UV Filter replacement required</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Sanitation sensor indicated UV lamp intensity drop below safety threshold. (Logged for Aditya Iyer at Hostel Block C).</t>
+          <t>2026-09-11 23:52:52</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Hostel Maintenance Operations</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:47:34</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TCK-1058</t>
+          <t>DEV-TCK-2058</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>STU-2026-157</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nisha Banerjee</t>
+          <t>Knip Dead Code Audit</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>SANITATION_FACILITIES</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>Automated Knip static analysis flagged 14 unused exports in legacy components (#58)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Run `knip --no-exit-code` and tree-shake unused mock data structures to reduce bundle size by 120KB. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Code Quality Team</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Mosquito breeding inspection requested around PG Residence garden</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Stagnant water near cooler drain pipes needs immediate fogging and larvicide treatment. (Logged for Nisha Banerjee at Hostel Block D).</t>
+          <t>2026-09-11 23:22:52</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Campus Sanitation Squad</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>2026-09-11 09:02:34</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TCK-1059</t>
+          <t>DEV-TCK-2059</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>STU-2026-158</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Tarun Chawla</t>
+          <t>Semgrep SAST Security</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>PHARMACY_MEDS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AI Voice Prescription</t>
+          <t>Semgrep security rule scanner flagged potential XSS target in unescaped innerHTML (#59)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Static analysis identified unescaped user note rendering in legacy support widget. Replace with DOMPurify. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Application Security Team</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Fulfillment of AI Voice-Parsed Prescription for Anti-Histamines &amp; Paracetamol</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Prescription parsed via AI Voice Modal. Requested hostel room delivery. (Logged for Tarun Chawla at PG Residence 1).</t>
+          <t>2026-09-11 22:52:52</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Campus Dispensary Pharmacy</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>2026-09-11 08:17:34</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TCK-1060</t>
+          <t>DEV-TCK-2060</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>STU-2026-159</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Pooja Agarwal</t>
+          <t>OWASP ZAP DAST Scan</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PHARMACY_MEDS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Cold Chain Insulin</t>
+          <t>OWASP ZAP dynamic application security test scan report remediation (#60)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Automated DAST scan flagged missing Strict-Transport-Security (HSTS) header on staging deployment. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>SecOps Team</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Cold-chain storage verification for student diabetes medication</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Insulin pen storage check at hostel pharmacy refrigeration unit. (Logged for Pooja Agarwal at Married Scholar Quarters).</t>
+          <t>2026-09-11 22:22:52</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Pharmacy Cold Chain Desk</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>2026-09-11 07:32:34</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TCK-1061</t>
+          <t>DEV-TCK-2061</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>STU-2026-160</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Database Connection Pool</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>INSURANCE_CLAIMS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Plan B Reimbursement</t>
+          <t>Scale BigQuery / PostgreSQL connection pool for 50,000 concurrent student logins (#61)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Database connection pool saturated during morning 09:00 AM class attendance peak. Need to adjust MaxConnections to 500. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DevOps &amp; Infrastructure Team</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Insurance claim adjudication for outpatient emergency clinic visit</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Student submitted ₹1,200 emergency OPD consultation receipt for Plan B 100% claim settlement. (Logged for Rohit Sharma at Hostel Block A).</t>
+          <t>2026-09-11 21:52:52</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Insurance Adjudication AI</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>2026-09-11 06:47:34</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TCK-1062</t>
+          <t>DEV-TCK-2062</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>STU-2026-161</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Redis Cache Layer</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>INSURANCE_CLAIMS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Claim Anomaly Review</t>
+          <t>Implement Redis cluster caching for live wearable sensor telemetry endpoints (#62)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Direct DB queries for live heart rate and step counter telemetry causing query latency. Need Redis L2 caching with 60s TTL. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Backend Engineering</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Duplicate bill anomaly flagged on hospitalization claim</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Claim Adjudication AI flagged potential double-entry invoice for review by signed officer. (Logged for Priya Patel at Hostel Block B).</t>
+          <t>2026-09-11 21:22:52</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Claims Compliance Officer</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>2026-09-11 06:02:34</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TCK-1063</t>
+          <t>DEV-TCK-2063</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>STU-2026-162</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ananya Deshmukh</t>
+          <t>Horizontal Pod Autoscaler</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EMERGENCY_SOS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ambulance Dispatch</t>
+          <t>Configure Kubernetes HPA for API Gateway under 10k RPS load (#63)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Auto-scaling trigger threshold set too high (85% CPU). Lower CPU target to 65% for instant pod spin-up. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>DevOps Team</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Emergency 24x7 Ambulance dispatch request for acute abdominal distress</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Student triggered 24x7 SOS emergency button. Campus medical team dispatched to Hostel Block A. (Logged for Ananya Deshmukh at Hostel Block C).</t>
+          <t>2026-09-11 20:52:52</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>24x7 Emergency Dispatch Unit</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>2026-09-11 05:17:34</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TCK-1064</t>
+          <t>DEV-TCK-2064</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>STU-2026-163</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>CDN Asset Optimization</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EMERGENCY_SOS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Crisis Intervention</t>
+          <t>Static media and bundle asset distribution via Cloudflare / CloudFront CDN (#64)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Static JS bundles exceeding 2.5MB payload on slow 3G mobile devices. Implement Brotli compression &amp; CDN edge caching. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Frontend Performance Team</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Panic attack emergency trigger from central library reading room</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>SOS trigger handled by Triage Council AI. Campus counselor dispatched. (Logged for Rahul Verma at Hostel Block D).</t>
+          <t>2026-09-11 20:22:52</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Crisis Response Team</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>2026-09-11 04:32:34</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TCK-1065</t>
+          <t>DEV-TCK-2065</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>STU-2026-164</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Aarav Mehta</t>
+          <t>WebSocket Heartbeat</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AI_DIAGNOSTICS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>4-Hr Scouting Anomaly</t>
+          <t>Real-time vitals camera streaming WebSocket socket reconnection stability (#65)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>WebSocket connections dropping after 5 minutes of idle posture coaching. Implement exponential backoff ping/pong heartbeat. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Realtime WebSockets Team</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4-Hour Scouting Loop Flagged Seasonal Flu Spike in Hostel Block D</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Automated 4-hour agent scouting loop detected 4 viral flu cases in 12 hours. (Logged for Aarav Mehta at PG Residence 1).</t>
+          <t>2026-09-11 19:52:52</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Automated 4-Hr Agent Loop</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>2026-09-11 03:47:34</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TCK-1066</t>
+          <t>DEV-TCK-2066</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>STU-2026-165</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sneha Kulkarni</t>
+          <t>Playwright E2E Automation</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AI_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Weather Alert Sync</t>
+          <t>Playwright End-to-End browser test suite failing on Signup Step 6 Plan Selection (#66)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Automated Playwright test `tests/e2e/signup_flow.spec.ts` failed due to missing plan selection modal selector `#plan-c-btn`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>QA Automation Team</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Monsoon High Humidity Weather Banner Triggered automatically</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Weather API updated microclimate alert to 85% humidity Dengue risk. (Logged for Sneha Kulkarni at Married Scholar Quarters).</t>
+          <t>2026-09-11 19:22:52</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Environmental Sensing Agent</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>2026-09-11 03:02:34</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TCK-1067</t>
+          <t>DEV-TCK-2067</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>STU-2026-166</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>Vitest Coverage Gate</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>General Fever</t>
+          <t>Vitest unit test coverage dropped below mandatory 85% threshold (#67)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>New health overview telemetry module added without unit test assertions. Need 100% coverage on `healthExperience.ts`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>QA Quality Engineers</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>High fever and shivering post-monsoon study session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Student reported 102.4°F temperature. Requested tele-consultation and fever meds. (Logged for Vikram Singh at Hostel Block A).</t>
+          <t>2026-09-11 18:52:52</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Campus Clinical Team</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>2026-09-11 02:17:34</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TCK-1068</t>
+          <t>DEV-TCK-2068</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>STU-2026-167</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Kavya Nair</t>
+          <t>API Contract Testing</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mental Health Tele-MANAS</t>
+          <t>OpenAPI schema validation mismatch on POST /api/v1/telemetry/vitals endpoint (#68)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Contract test flagged missing `sensorAccuracyIndex` field in JSON request payload. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Backend QA Team</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Exam anxiety &amp; acute sleep deprivation support request</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Student requested confidential 24x7 counseling via Tele-MANAS regarding end-semester stress. (Logged for Kavya Nair at Hostel Block B).</t>
+          <t>2026-09-11 18:22:52</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Tele-MANAS Counseling Desk</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>2026-09-11 01:32:34</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TCK-1069</t>
+          <t>DEV-TCK-2069</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>STU-2026-168</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Devansh Gupta</t>
+          <t>Mock Service Worker (MSW)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>MSW mock server latency simulation for offline mode PWA testing (#69)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Mock service worker failing to intercept offline PWA sync requests in Vitest runner. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>QA Tooling Team</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Allergic skin rash on arms after hostel outdoor event</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Red itchy rash spreading on forearms. Needs video evaluation with dermatologist. (Logged for Devansh Gupta at Hostel Block C).</t>
+          <t>2026-09-11 17:52:52</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Dermatology On-Call Doctor</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>2026-09-11 00:47:34</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TCK-1070</t>
+          <t>DEV-TCK-2070</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>STU-2026-169</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Isha Sundaram</t>
+          <t>Visual Regression Test</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Percy / Chromatic visual regression diff detected on InterfaceBar theme header (#70)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Dark mode pill buttons shifted 2px out of alignment on 1440px viewport displays. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Frontend QA Team</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Severe dry eye &amp; screen glare fatigue after 10hr coding session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Eye strain and burning sensation. Needs artificial tear prescription. (Logged for Isha Sundaram at Hostel Block D).</t>
+          <t>2026-09-11 17:22:52</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Digital Ergonomics Desk</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>2026-09-11 00:02:34</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TCK-1071</t>
+          <t>DEV-TCK-2071</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>STU-2026-170</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Crisis Gate Safety</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>ESCALATED</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Orthopedics</t>
+          <t>Crisis Gate AI deterministic bypass latency under 10ms for URGENT_EMERGENCY prompts (#71)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Crisis detection gate must process self-harm / panic keywords strictly on-device in &lt;10ms without hitting remote LLM. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>AI Safety &amp; Ethics Team</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Sprained ankle during campus badminton tournament</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Swollen right ankle. Requested cold compress guidance and X-ray slot. (Logged for Arjun Reddy at PG Residence 1).</t>
+          <t>2026-09-11 16:52:52</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Sports Medicine Unit</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>2026-09-10 23:17:34</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TCK-1072</t>
+          <t>DEV-TCK-2072</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>STU-2026-171</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Meera Rao</t>
+          <t>AI Voice Prescription</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Heart Rate Alert</t>
+          <t>Optimize Speech-to-Text Whisper model latency for medical dosage parsing (#72)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Voice prescription recording parsing taking &gt;3.2 seconds. Need streaming chunk parsing via WebSockets. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Speech Team</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Resting Heart Rate Spike (138 BPM) detected by Smart Watch</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Wearable sensor triggered resting tachycardia alert while student was seated in library. (Logged for Meera Rao at Married Scholar Quarters).</t>
+          <t>2026-09-11 16:22:52</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Vitals Monitoring AI</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>2026-09-10 22:32:34</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TCK-1073</t>
+          <t>DEV-TCK-2073</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>STU-2026-172</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Siddharth Joshi</t>
+          <t>RAG Vector Store</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SpO2 Telemetry</t>
+          <t>Vector DB embedding index sync for 1,000+ medical guidelines &amp; drug interactions (#73)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Pinecone / Qdrant vector index out of sync with new NABL lab test reference values. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>AI Data Engineering</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Low Blood Oxygen SpO2 (92%) alert during night study</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>RPPG Vitals Camera &amp; Wearables flagged drop in peripheral oxygen saturation. (Logged for Siddharth Joshi at Hostel Block A).</t>
+          <t>2026-09-11 15:52:52</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Emergency Response Desk</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>2026-09-10 21:47:34</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TCK-1074</t>
+          <t>DEV-TCK-2074</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>STU-2026-173</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Tanvi Saxena</t>
+          <t>Prompt Injection Defense</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Posture Coach</t>
+          <t>Harden AI Health Assistant system prompt against jailbreak injection attacks (#74)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Red team security scan identified prompt bypass attempt targeting system constitution rules. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Security Team</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Chronic Slouch Posture warning (3.5 hours continuous neck tilt)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Study Posture Coach sensor alerted lumbar strain risk during project coding. (Logged for Tanvi Saxena at Hostel Block B).</t>
+          <t>2026-09-11 15:22:52</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Student Wellness AI</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>2026-09-10 21:02:34</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TCK-1075</t>
+          <t>DEV-TCK-2075</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>STU-2026-174</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Karan Bhatia</t>
+          <t>LLM Token Budget</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Step Counter</t>
+          <t>Implement token capping and fallback model switching (Gemini Pro to Flash) (#75)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>High token consumption on long multi-turn patient chats. Implement auto-summarization at 4,000 tokens. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Infra Team</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Zero mobility alert (Under 500 steps for 48 hours straight)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Mobile Step Counter sensor flagged severe sedentary lock during exam preparation. (Logged for Karan Bhatia at Hostel Block C).</t>
+          <t>2026-09-11 14:52:52</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Health Coach Agent</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>2026-09-10 20:17:34</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TCK-1076</t>
+          <t>DEV-TCK-2076</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>STU-2026-175</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Riya Sen</t>
+          <t>4-Hr Scouting Agent Cron</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Monsoon Dengue NS1</t>
+          <t>4-Hour AI Scouting Agent background cron schedule execution monitoring (#76)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Background schedule task `task-524` verified running on `0 */4 * * *` cron schedule pulling campus telemetry. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Automation &amp; Agent Ops</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>NABL Dengue NS1 Antigen &amp; Complete Blood Count (CBC) home sample collection</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Fever suspect requested hostel room sample collection for CBC platelet count check. (Logged for Riya Sen at Hostel Block D).</t>
+          <t>2026-09-11 14:22:52</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Pathology Lab Partner</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>2026-09-10 19:32:34</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TCK-1077</t>
+          <t>DEV-TCK-2077</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>STU-2026-176</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Aditya Iyer</t>
+          <t>GitHub Actions CI Gate</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitamin D3 &amp; B12</t>
+          <t>GitHub Actions CI pipeline execution time optimization (Reduce from 8m to 2m) (#77)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Cache node_modules and Vitest transform files to accelerate pull request quality gate checks. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>DevOps &amp; CI/CD Team</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Routine Vitamin D3 &amp; Serum B12 deficiency panel booking</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Student booked discounted lab package under Studentkare Plan B membership. (Logged for Aditya Iyer at PG Residence 1).</t>
+          <t>2026-09-11 13:52:52</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Diagnostic Services Unit</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>2026-09-10 18:47:34</t>
-        </is>
-      </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TCK-1078</t>
+          <t>DEV-TCK-2078</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>STU-2026-177</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nisha Banerjee</t>
+          <t>Knip Dead Code Audit</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>ESCALATED</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Water Bacteria Test</t>
+          <t>Automated Knip static analysis flagged 14 unused exports in legacy components (#78)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Run `knip --no-exit-code` and tree-shake unused mock data structures to reduce bundle size by 120KB. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>ESCALATED</t>
+          <t>Code Quality Team</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Hostel Block C Water Dispenser Bacterial Culture Test</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Randomized 4-hour water sample collected to verify E. coli and coliform absence. (Logged for Nisha Banerjee at Married Scholar Quarters).</t>
+          <t>2026-09-11 13:22:52</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Environmental Safety Lab</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>2026-09-10 18:02:34</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TCK-1079</t>
+          <t>DEV-TCK-2079</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STU-2026-178</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Tarun Chawla</t>
+          <t>Semgrep SAST Security</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>SANITATION_FACILITIES</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Water Purifier</t>
+          <t>Semgrep security rule scanner flagged potential XSS target in unescaped innerHTML (#79)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Static analysis identified unescaped user note rendering in legacy support widget. Replace with DOMPurify. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Application Security Team</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Hostel Block B 2nd Floor RO UV Filter replacement required</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Sanitation sensor indicated UV lamp intensity drop below safety threshold. (Logged for Tarun Chawla at Hostel Block A).</t>
+          <t>2026-09-11 12:52:52</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Hostel Maintenance Operations</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>2026-09-10 17:17:34</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TCK-1080</t>
+          <t>DEV-TCK-2080</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>STU-2026-179</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pooja Agarwal</t>
+          <t>OWASP ZAP DAST Scan</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SANITATION_FACILITIES</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pest Control</t>
+          <t>OWASP ZAP dynamic application security test scan report remediation (#80)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Automated DAST scan flagged missing Strict-Transport-Security (HSTS) header on staging deployment. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>SecOps Team</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Mosquito breeding inspection requested around PG Residence garden</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Stagnant water near cooler drain pipes needs immediate fogging and larvicide treatment. (Logged for Pooja Agarwal at Hostel Block B).</t>
+          <t>2026-09-11 12:22:52</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Campus Sanitation Squad</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>2026-09-10 16:32:34</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TCK-1081</t>
+          <t>DEV-TCK-2081</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>STU-2026-180</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Rohit Sharma</t>
+          <t>Database Connection Pool</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PHARMACY_MEDS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AI Voice Prescription</t>
+          <t>Scale BigQuery / PostgreSQL connection pool for 50,000 concurrent student logins (#81)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Database connection pool saturated during morning 09:00 AM class attendance peak. Need to adjust MaxConnections to 500. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>DevOps &amp; Infrastructure Team</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Fulfillment of AI Voice-Parsed Prescription for Anti-Histamines &amp; Paracetamol</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Prescription parsed via AI Voice Modal. Requested hostel room delivery. (Logged for Rohit Sharma at Hostel Block C).</t>
+          <t>2026-09-11 11:52:52</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Campus Dispensary Pharmacy</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:47:34</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TCK-1082</t>
+          <t>DEV-TCK-2082</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>STU-2026-181</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Priya Patel</t>
+          <t>Redis Cache Layer</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PHARMACY_MEDS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Cold Chain Insulin</t>
+          <t>Implement Redis cluster caching for live wearable sensor telemetry endpoints (#82)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Direct DB queries for live heart rate and step counter telemetry causing query latency. Need Redis L2 caching with 60s TTL. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Backend Engineering</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Cold-chain storage verification for student diabetes medication</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Insulin pen storage check at hostel pharmacy refrigeration unit. (Logged for Priya Patel at Hostel Block D).</t>
+          <t>2026-09-11 11:22:52</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Pharmacy Cold Chain Desk</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>2026-09-10 15:02:34</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TCK-1083</t>
+          <t>DEV-TCK-2083</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>STU-2026-182</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ananya Deshmukh</t>
+          <t>Horizontal Pod Autoscaler</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>INSURANCE_CLAIMS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Plan B Reimbursement</t>
+          <t>Configure Kubernetes HPA for API Gateway under 10k RPS load (#83)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Auto-scaling trigger threshold set too high (85% CPU). Lower CPU target to 65% for instant pod spin-up. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>DevOps Team</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Insurance claim adjudication for outpatient emergency clinic visit</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Student submitted ₹1,200 emergency OPD consultation receipt for Plan B 100% claim settlement. (Logged for Ananya Deshmukh at PG Residence 1).</t>
+          <t>2026-09-11 10:52:52</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Insurance Adjudication AI</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>2026-09-10 14:17:34</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TCK-1084</t>
+          <t>DEV-TCK-2084</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>STU-2026-183</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rahul Verma</t>
+          <t>CDN Asset Optimization</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>INSURANCE_CLAIMS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Claim Anomaly Review</t>
+          <t>Static media and bundle asset distribution via Cloudflare / CloudFront CDN (#84)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Static JS bundles exceeding 2.5MB payload on slow 3G mobile devices. Implement Brotli compression &amp; CDN edge caching. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Frontend Performance Team</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Duplicate bill anomaly flagged on hospitalization claim</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Claim Adjudication AI flagged potential double-entry invoice for review by signed officer. (Logged for Rahul Verma at Married Scholar Quarters).</t>
+          <t>2026-09-11 10:22:52</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Claims Compliance Officer</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>2026-09-10 13:32:34</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>TCK-1085</t>
+          <t>DEV-TCK-2085</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STU-2026-184</t>
+          <t>Development Scaling &amp; Infrastructure</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Aarav Mehta</t>
+          <t>WebSocket Heartbeat</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>EMERGENCY_SOS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ambulance Dispatch</t>
+          <t>Real-time vitals camera streaming WebSocket socket reconnection stability (#85)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>WebSocket connections dropping after 5 minutes of idle posture coaching. Implement exponential backoff ping/pong heartbeat. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Realtime WebSockets Team</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Emergency 24x7 Ambulance dispatch request for acute abdominal distress</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Student triggered 24x7 SOS emergency button. Campus medical team dispatched to Hostel Block A. (Logged for Aarav Mehta at Hostel Block A).</t>
+          <t>2026-09-11 09:52:52</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>24x7 Emergency Dispatch Unit</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>2026-09-10 12:47:34</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>TCK-1086</t>
+          <t>DEV-TCK-2086</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>STU-2026-185</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sneha Kulkarni</t>
+          <t>Playwright E2E Automation</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>EMERGENCY_SOS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Crisis Intervention</t>
+          <t>Playwright End-to-End browser test suite failing on Signup Step 6 Plan Selection (#86)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Automated Playwright test `tests/e2e/signup_flow.spec.ts` failed due to missing plan selection modal selector `#plan-c-btn`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>QA Automation Team</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Panic attack emergency trigger from central library reading room</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>SOS trigger handled by Triage Council AI. Campus counselor dispatched. (Logged for Sneha Kulkarni at Hostel Block B).</t>
+          <t>2026-09-11 09:22:52</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Crisis Response Team</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>2026-09-10 12:02:34</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>TCK-1087</t>
+          <t>DEV-TCK-2087</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>STU-2026-186</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Vikram Singh</t>
+          <t>Vitest Coverage Gate</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AI_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>4-Hr Scouting Anomaly</t>
+          <t>Vitest unit test coverage dropped below mandatory 85% threshold (#87)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>New health overview telemetry module added without unit test assertions. Need 100% coverage on `healthExperience.ts`. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>QA Quality Engineers</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>4-Hour Scouting Loop Flagged Seasonal Flu Spike in Hostel Block D</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Automated 4-hour agent scouting loop detected 4 viral flu cases in 12 hours. (Logged for Vikram Singh at Hostel Block C).</t>
+          <t>2026-09-11 08:52:52</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Automated 4-Hr Agent Loop</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>2026-09-10 11:17:34</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>TCK-1088</t>
+          <t>DEV-TCK-2088</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>STU-2026-187</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kavya Nair</t>
+          <t>API Contract Testing</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AI_DIAGNOSTICS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Weather Alert Sync</t>
+          <t>OpenAPI schema validation mismatch on POST /api/v1/telemetry/vitals endpoint (#88)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Contract test flagged missing `sensorAccuracyIndex` field in JSON request payload. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>Backend QA Team</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Monsoon High Humidity Weather Banner Triggered automatically</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Weather API updated microclimate alert to 85% humidity Dengue risk. (Logged for Kavya Nair at Hostel Block D).</t>
+          <t>2026-09-11 08:22:52</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Environmental Sensing Agent</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>2026-09-10 10:32:34</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TCK-1089</t>
+          <t>DEV-TCK-2089</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>STU-2026-188</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Devansh Gupta</t>
+          <t>Mock Service Worker (MSW)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>General Fever</t>
+          <t>MSW mock server latency simulation for offline mode PWA testing (#89)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Mock service worker failing to intercept offline PWA sync requests in Vitest runner. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>QA Tooling Team</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>High fever and shivering post-monsoon study session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Student reported 102.4°F temperature. Requested tele-consultation and fever meds. (Logged for Devansh Gupta at PG Residence 1).</t>
+          <t>2026-09-11 07:52:52</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Campus Clinical Team</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>2026-09-10 09:47:34</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>TCK-1090</t>
+          <t>DEV-TCK-2090</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>STU-2026-189</t>
+          <t>QA Backend &amp; Test Automation</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Isha Sundaram</t>
+          <t>Visual Regression Test</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mental Health Tele-MANAS</t>
+          <t>Percy / Chromatic visual regression diff detected on InterfaceBar theme header (#90)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Dark mode pill buttons shifted 2px out of alignment on 1440px viewport displays. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Frontend QA Team</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Exam anxiety &amp; acute sleep deprivation support request</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Student requested confidential 24x7 counseling via Tele-MANAS regarding end-semester stress. (Logged for Isha Sundaram at Married Scholar Quarters).</t>
+          <t>2026-09-11 07:22:52</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Tele-MANAS Counseling Desk</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>2026-09-10 09:02:34</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TCK-1091</t>
+          <t>DEV-TCK-2091</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>STU-2026-190</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Arjun Reddy</t>
+          <t>Crisis Gate Safety</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dermatology</t>
+          <t>Crisis Gate AI deterministic bypass latency under 10ms for URGENT_EMERGENCY prompts (#91)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Crisis detection gate must process self-harm / panic keywords strictly on-device in &lt;10ms without hitting remote LLM. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>AI Safety &amp; Ethics Team</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Allergic skin rash on arms after hostel outdoor event</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Red itchy rash spreading on forearms. Needs video evaluation with dermatologist. (Logged for Arjun Reddy at Hostel Block A).</t>
+          <t>2026-09-11 06:52:52</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Dermatology On-Call Doctor</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>2026-09-10 08:17:34</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>TCK-1092</t>
+          <t>DEV-TCK-2092</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>STU-2026-191</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Meera Rao</t>
+          <t>AI Voice Prescription</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>ESCALATED</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>Optimize Speech-to-Text Whisper model latency for medical dosage parsing (#92)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Voice prescription recording parsing taking &gt;3.2 seconds. Need streaming chunk parsing via WebSockets. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>ESCALATED</t>
+          <t>AI Speech Team</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Severe dry eye &amp; screen glare fatigue after 10hr coding session</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Eye strain and burning sensation. Needs artificial tear prescription. (Logged for Meera Rao at Hostel Block B).</t>
+          <t>2026-09-11 06:22:52</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Digital Ergonomics Desk</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>2026-09-10 07:32:34</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TCK-1093</t>
+          <t>DEV-TCK-2093</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>STU-2026-192</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Siddharth Joshi</t>
+          <t>RAG Vector Store</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>TELE_HEALTH</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Orthopedics</t>
+          <t>Vector DB embedding index sync for 1,000+ medical guidelines &amp; drug interactions (#93)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Pinecone / Qdrant vector index out of sync with new NABL lab test reference values. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Data Engineering</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Sprained ankle during campus badminton tournament</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Swollen right ankle. Requested cold compress guidance and X-ray slot. (Logged for Siddharth Joshi at Hostel Block C).</t>
+          <t>2026-09-11 05:52:52</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Sports Medicine Unit</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>2026-09-10 06:47:34</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Pending sprint execution / code review.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>TCK-1094</t>
+          <t>DEV-TCK-2094</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>STU-2026-193</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Tanvi Saxena</t>
+          <t>Prompt Injection Defense</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Heart Rate Alert</t>
+          <t>Harden AI Health Assistant system prompt against jailbreak injection attacks (#94)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>Red team security scan identified prompt bypass attempt targeting system constitution rules. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>AI Security Team</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Resting Heart Rate Spike (138 BPM) detected by Smart Watch</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Wearable sensor triggered resting tachycardia alert while student was seated in library. (Logged for Tanvi Saxena at Hostel Block D).</t>
+          <t>2026-09-11 05:22:52</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Vitals Monitoring AI</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>2026-09-10 06:02:34</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>TCK-1095</t>
+          <t>DEV-TCK-2095</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>STU-2026-194</t>
+          <t>AI Architecture &amp; LLM Engineering</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Karan Bhatia</t>
+          <t>LLM Token Budget</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>PG Residence 1</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SpO2 Telemetry</t>
+          <t>Implement token capping and fallback model switching (Gemini Pro to Flash) (#95)</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>CRITICAL</t>
+          <t>High token consumption on long multi-turn patient chats. Implement auto-summarization at 4,000 tokens. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>AI Infra Team</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Low Blood Oxygen SpO2 (92%) alert during night study</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>RPPG Vitals Camera &amp; Wearables flagged drop in peripheral oxygen saturation. (Logged for Karan Bhatia at PG Residence 1).</t>
+          <t>2026-09-11 04:52:52</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Emergency Response Desk</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>2026-09-10 05:17:34</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>TCK-1096</t>
+          <t>DEV-TCK-2096</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>STU-2026-195</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Riya Sen</t>
+          <t>4-Hr Scouting Agent Cron</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Married Scholar Quarters</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Posture Coach</t>
+          <t>4-Hour AI Scouting Agent background cron schedule execution monitoring (#96)</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Background schedule task `task-524` verified running on `0 */4 * * *` cron schedule pulling campus telemetry. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>Automation &amp; Agent Ops</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Chronic Slouch Posture warning (3.5 hours continuous neck tilt)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Study Posture Coach sensor alerted lumbar strain risk during project coding. (Logged for Riya Sen at Married Scholar Quarters).</t>
+          <t>2026-09-11 04:22:52</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Student Wellness AI</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>2026-09-10 04:32:34</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>TCK-1097</t>
+          <t>DEV-TCK-2097</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>STU-2026-196</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Aditya Iyer</t>
+          <t>GitHub Actions CI Gate</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Hostel Block A</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SMART_SENSORS</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Step Counter</t>
+          <t>GitHub Actions CI pipeline execution time optimization (Reduce from 8m to 2m) (#97)</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>Cache node_modules and Vitest transform files to accelerate pull request quality gate checks. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>DevOps &amp; CI/CD Team</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Zero mobility alert (Under 500 steps for 48 hours straight)</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Mobile Step Counter sensor flagged severe sedentary lock during exam preparation. (Logged for Aditya Iyer at Hostel Block A).</t>
+          <t>2026-09-11 03:52:52</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Health Coach Agent</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>2026-09-10 03:47:34</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>TCK-1098</t>
+          <t>DEV-TCK-2098</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>STU-2026-197</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Nisha Banerjee</t>
+          <t>Knip Dead Code Audit</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Hostel Block B</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>RESOLVED</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Monsoon Dengue NS1</t>
+          <t>Automated Knip static analysis flagged 14 unused exports in legacy components (#98)</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Run `knip --no-exit-code` and tree-shake unused mock data structures to reduce bundle size by 120KB. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>RESOLVED</t>
+          <t>Code Quality Team</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>NABL Dengue NS1 Antigen &amp; Complete Blood Count (CBC) home sample collection</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Fever suspect requested hostel room sample collection for CBC platelet count check. (Logged for Nisha Banerjee at Hostel Block B).</t>
+          <t>2026-09-11 03:22:52</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Pathology Lab Partner</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>2026-09-10 03:02:34</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>Processed cleanly by automated workflow &amp; clinical officer.</t>
+          <t>Automated PR merged, passed Vitest regression test suite &amp; deployed to staging.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>TCK-1099</t>
+          <t>DEV-TCK-2099</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>STU-2026-198</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tarun Chawla</t>
+          <t>Semgrep SAST Security</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Hostel Block C</t>
+          <t>CRITICAL</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>ESCALATED</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitamin D3 &amp; B12</t>
+          <t>Semgrep security rule scanner flagged potential XSS target in unescaped innerHTML (#99)</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>Static analysis identified unescaped user note rendering in legacy support widget. Replace with DOMPurify. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>ESCALATED</t>
+          <t>Application Security Team</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Routine Vitamin D3 &amp; Serum B12 deficiency panel booking</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Student booked discounted lab package under Studentkare Plan B membership. (Logged for Tarun Chawla at Hostel Block C).</t>
+          <t>2026-09-11 02:52:52</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Diagnostic Services Unit</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>2026-09-10 02:17:34</t>
-        </is>
-      </c>
-      <c r="N100" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TCK-1100</t>
+          <t>DEV-TCK-2100</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>STU-2026-199</t>
+          <t>Automation, CI/CD &amp; SecOps</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pooja Agarwal</t>
+          <t>OWASP ZAP DAST Scan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Hostel Block D</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>LAB_DIAGNOSTICS</t>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Water Bacteria Test</t>
+          <t>OWASP ZAP dynamic application security test scan report remediation (#100)</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>Automated DAST scan flagged missing Strict-Transport-Security (HSTS) header on staging deployment. [Target Environment: Production / Staging Kubernetes Cluster]</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>IN_PROGRESS</t>
+          <t>SecOps Team</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Hostel Block C Water Dispenser Bacterial Culture Test</t>
+          <t>Yes (CI/CD Quality Gate Verified)</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Randomized 4-hour water sample collected to verify E. coli and coliform absence. (Logged for Pooja Agarwal at Hostel Block D).</t>
+          <t>2026-09-11 02:22:52</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Environmental Safety Lab</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>2026-09-10 01:32:34</t>
-        </is>
-      </c>
-      <c r="N101" t="inlineStr"/>
+          <t>Pending sprint execution / code review.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
